--- a/templates/INFRA GER ADV SB - template.xlsx
+++ b/templates/INFRA GER ADV SB - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$11</definedName>
@@ -1424,96 +1424,96 @@
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>1.00240483</v>
+        <v>0.98952841</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>-0.001294654238198634</v>
+        <v>0.009738744973530666</v>
       </c>
       <c r="E20" s="33" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="34" t="n">
-        <v>-2.385745417339002</v>
+        <v>17.94623267410901</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>1.00370428</v>
+        <v>0.97998459</v>
       </c>
       <c r="D21" s="37" t="n">
-        <v>0.001820606804056712</v>
+        <v>0.0007279286878234537</v>
       </c>
       <c r="E21" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="38" t="n">
-        <v>3.3549531692709</v>
+        <v>1.341402576753431</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>1.00188025</v>
+        <v>0.97927175</v>
       </c>
       <c r="D22" s="37" t="n">
-        <v>-0.0003781556480706438</v>
+        <v>0.002184062875401294</v>
       </c>
       <c r="E22" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="38" t="n">
-        <v>-0.696852547812832</v>
+        <v>4.024717830004459</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>1.00225926</v>
+        <v>0.97713762</v>
       </c>
       <c r="D23" s="37" t="n">
-        <v>-0.00202737174903167</v>
+        <v>-0.01332616754256055</v>
       </c>
       <c r="E23" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F23" s="38" t="n">
-        <v>-3.73597267655395</v>
+        <v>-24.55701468956821</v>
       </c>
     </row>
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B24" s="35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C24" s="36" t="n">
-        <v>1.00429534</v>
+        <v>0.99033499</v>
       </c>
       <c r="D24" s="37" t="n">
-        <v>-0.0005715765934627415</v>
+        <v>-0.007400732254389419</v>
       </c>
       <c r="E24" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>-1.053282180120401</v>
+        <v>-13.63782123436232</v>
       </c>
     </row>
     <row r="25" ht="15.95" customHeight="1">
@@ -1553,18 +1553,18 @@
     <row r="27" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B27" s="51" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr"/>
       <c r="D27" s="37" t="n">
-        <v>-0.000878015079512906</v>
+        <v>-0.01977675127779488</v>
       </c>
       <c r="E27" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>-0.08375315301941147</v>
+        <v>-5.197806679494311</v>
       </c>
       <c r="G27" s="53" t="n"/>
     </row>
@@ -1576,13 +1576,13 @@
       </c>
       <c r="C28" s="51" t="inlineStr"/>
       <c r="D28" s="37" t="n">
-        <v>0.001159847683012138</v>
+        <v>-0.01902421754953643</v>
       </c>
       <c r="E28" s="37" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>0.1000053610558554</v>
+        <v>-1.652782102341601</v>
       </c>
       <c r="G28" s="53" t="n"/>
     </row>
@@ -1594,13 +1594,13 @@
       </c>
       <c r="C29" s="39" t="inlineStr"/>
       <c r="D29" s="37" t="n">
-        <v>0.002404829999999913</v>
+        <v>-0.01047158999999998</v>
       </c>
       <c r="E29" s="37" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>0.181197230051206</v>
+        <v>-0.5574743942099972</v>
       </c>
       <c r="G29" s="40" t="n"/>
     </row>
@@ -1612,13 +1612,13 @@
       </c>
       <c r="C30" s="39" t="inlineStr"/>
       <c r="D30" s="37" t="n">
-        <v>0.002404829999999913</v>
+        <v>-0.01047158999999998</v>
       </c>
       <c r="E30" s="37" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>0.181197230051206</v>
+        <v>-0.5574743942099972</v>
       </c>
       <c r="G30" s="40" t="n"/>
     </row>
@@ -1646,7 +1646,7 @@
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="41" t="n">
-        <v>21260064.07</v>
+        <v>27468215.92</v>
       </c>
       <c r="F33" s="25" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -1661,7 +1661,7 @@
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="41" t="n">
-        <v>21898883.148</v>
+        <v>22936315.51714286</v>
       </c>
       <c r="F34" s="25" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D36" s="17" t="n"/>
